--- a/stick-world/config/excel/制造.xlsx
+++ b/stick-world/config/excel/制造.xlsx
@@ -554,10 +554,8 @@
           <t>economy</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="F4" t="n">
+        <v>10</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -586,10 +584,8 @@
           <t>military</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="F5" t="n">
+        <v>20</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -618,10 +614,8 @@
           <t>administration</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="F6" t="n">
+        <v>10</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -655,10 +649,8 @@
           <t>tech_stone_tools</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="F7" t="n">
+        <v>40</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -692,10 +684,8 @@
           <t>tech_basic_combat</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
+      <c r="F8" t="n">
+        <v>40</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -729,10 +719,8 @@
           <t>tech_primitive_administration</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
+      <c r="F9" t="n">
+        <v>30</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -766,10 +754,8 @@
           <t>tech_primitive_administration</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
+      <c r="F10" t="n">
+        <v>40</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -803,10 +789,8 @@
           <t>tech_bronze_working</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="F11" t="n">
+        <v>80</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -840,10 +824,8 @@
           <t>tech_formation_tactics,tech_bronze_working</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
+      <c r="F12" t="n">
+        <v>90</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -877,10 +859,8 @@
           <t>tech_early_writing,tech_herbal_medicine</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
+      <c r="F13" t="n">
+        <v>70</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -914,10 +894,8 @@
           <t>tech_early_writing</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="F14" t="n">
+        <v>60</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -951,10 +929,8 @@
           <t>tech_early_writing,tech_bronze_working</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
+      <c r="F15" t="n">
+        <v>80</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/stick-world/config/excel/制造.xlsx
+++ b/stick-world/config/excel/制造.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
